--- a/data_src/xlsx表/banner_config.xlsx
+++ b/data_src/xlsx表/banner_config.xlsx
@@ -560,7 +560,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
